--- a/yellow-server/data/results/shopping.xlsx
+++ b/yellow-server/data/results/shopping.xlsx
@@ -64,8 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:S11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,12 +440,30 @@
       <c r="M1" t="str">
         <v>异常购物</v>
       </c>
+      <c r="N1" t="str">
+        <v>异常资金</v>
+      </c>
+      <c r="O1" t="str">
+        <v>入住次数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>同住男人数</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>前科次数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前科人员</v>
+      </c>
+      <c r="S1" t="str">
+        <v>前科情况</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>张三</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" s="1" t="str">
         <v>310227199002301001</v>
       </c>
       <c r="C2">
@@ -479,13 +498,31 @@
       </c>
       <c r="M2" t="str">
         <v>高</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>老王</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" s="1" t="str">
         <v>310227199002301002</v>
       </c>
       <c r="C3">
@@ -520,13 +557,31 @@
       </c>
       <c r="M3" t="str">
         <v>高</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>老张</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4" s="1" t="str">
         <v>310227199002301003</v>
       </c>
       <c r="C4">
@@ -561,13 +616,31 @@
       </c>
       <c r="M4" t="str">
         <v>低</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>老李</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5" s="1" t="str">
         <v>310227199002301004</v>
       </c>
       <c r="C5">
@@ -602,13 +675,31 @@
       </c>
       <c r="M5" t="str">
         <v>低</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>小王</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B6" s="1" t="str">
         <v>310227199002301005</v>
       </c>
       <c r="C6">
@@ -643,13 +734,31 @@
       </c>
       <c r="M6" t="str">
         <v>低</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>小李</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B7" s="1" t="str">
         <v>310227199002301006</v>
       </c>
       <c r="C7">
@@ -684,13 +793,31 @@
       </c>
       <c r="M7" t="str">
         <v>低</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>小胡</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B8" s="1" t="str">
         <v>310227199002301007</v>
       </c>
       <c r="C8">
@@ -725,13 +852,31 @@
       </c>
       <c r="M8" t="str">
         <v>低</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>小刚</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B9" s="1" t="str">
         <v>310227199002301008</v>
       </c>
       <c r="C9">
@@ -766,13 +911,31 @@
       </c>
       <c r="M9" t="str">
         <v>中</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>小金</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B10" s="1" t="str">
         <v>310227199002301009</v>
       </c>
       <c r="C10">
@@ -807,13 +970,31 @@
       </c>
       <c r="M10" t="str">
         <v>中</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>小钱</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B11" s="1" t="str">
         <v>310227199002301010</v>
       </c>
       <c r="C11">
@@ -848,11 +1029,29 @@
       </c>
       <c r="M11" t="str">
         <v>中</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/yellow-server/data/results/shopping.xlsx
+++ b/yellow-server/data/results/shopping.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:M11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,24 +440,6 @@
       <c r="M1" t="str">
         <v>异常购物</v>
       </c>
-      <c r="N1" t="str">
-        <v>异常资金</v>
-      </c>
-      <c r="O1" t="str">
-        <v>入住次数</v>
-      </c>
-      <c r="P1" t="str">
-        <v>同住男人数</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>前科次数</v>
-      </c>
-      <c r="R1" t="str">
-        <v>前科人员</v>
-      </c>
-      <c r="S1" t="str">
-        <v>前科情况</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -499,24 +481,6 @@
       <c r="M2" t="str">
         <v>高</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -558,24 +522,6 @@
       <c r="M3" t="str">
         <v>高</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -617,24 +563,6 @@
       <c r="M4" t="str">
         <v>低</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -676,24 +604,6 @@
       <c r="M5" t="str">
         <v>低</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -735,24 +645,6 @@
       <c r="M6" t="str">
         <v>低</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -792,25 +684,7 @@
         <v>15507468291</v>
       </c>
       <c r="M7" t="str">
-        <v>低</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
+        <v>中</v>
       </c>
     </row>
     <row r="8">
@@ -851,25 +725,7 @@
         <v>18936274085</v>
       </c>
       <c r="M8" t="str">
-        <v>低</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
+        <v>中</v>
       </c>
     </row>
     <row r="9">
@@ -912,24 +768,6 @@
       <c r="M9" t="str">
         <v>中</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -971,24 +809,6 @@
       <c r="M10" t="str">
         <v>中</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1030,28 +850,10 @@
       <c r="M11" t="str">
         <v>中</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
   </ignoredErrors>
 </worksheet>
 </file>